--- a/finance/cogs/kit-cost-calculator.xlsx
+++ b/finance/cogs/kit-cost-calculator.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +74,20 @@
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +107,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +159,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -544,12 +563,12 @@
           <t>Mailer box</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Researched range $0.60-$4.50. Plain mailer is cheapest.</t>
+      <c r="B5" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>CONFIRMED - BoxUp order 1086099. True landed cost incl. tax + freight ($4,385.70 / 3000).</t>
         </is>
       </c>
     </row>
@@ -931,6 +950,13 @@
       <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Internal planning only. Not tax, accounting, or legal advice. For review by a licensed professional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>GREEN cells are CONFIRMED real costs from a receipt. Yellow cells still need your numbers.</t>
         </is>
       </c>
     </row>

--- a/finance/cogs/kit-cost-calculator.xlsx
+++ b/finance/cogs/kit-cost-calculator.xlsx
@@ -578,12 +578,12 @@
           <t>Collectible flash cards (5+)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>NEEDS A QUOTE - deck pricing does not apply to 5-card sets</t>
+      <c r="B6" s="17" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>CONFIRMED $0.71 each at Office Depot, colour both sides on cardstock. Shown as 8 cards - CONFIRM THE COUNT.</t>
         </is>
       </c>
     </row>

--- a/finance/cogs/kit-cost-calculator.xlsx
+++ b/finance/cogs/kit-cost-calculator.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +86,20 @@
       <color rgb="00006100"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +124,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,6 +178,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -578,12 +597,12 @@
           <t>Collectible flash cards (5+)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>CONFIRMED $0.71 each at Office Depot, colour both sides on cardstock. Shown as 8 cards - CONFIRM THE COUNT.</t>
+      <c r="B6" s="19" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>CEILING, not your real cost. 7 cards x $0.71 TRIAL printing at Office Depot. Bulk should come in lower - get a quote.</t>
         </is>
       </c>
     </row>
@@ -957,6 +976,13 @@
       <c r="A43" s="18" t="inlineStr">
         <is>
           <t>GREEN cells are CONFIRMED real costs from a receipt. Yellow cells still need your numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>AMBER cells are real but PROVISIONAL - a trial price or a placeholder. Treat as a ceiling, replace with a production quote.</t>
         </is>
       </c>
     </row>
